--- a/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 정말 많이 피곤해서예요, 정상적인 수준 이상으로요. 잠은 잘 자고 직장에서도 여전히 잘 해내고 있는데, 하루가 제대로 시작되기도 전에 배터리가 낮은 상태로 돌아가고 있는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요즘 슬프거나 가라앉는 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네... 그런 것 같아요. 항상 울고 있는 건 아니지만, 꽤 오랫동안 대부분의 날이 뭔가 회색빛에 밋밋하게 느껴졌어요. 예전에 기대하던 일들—낚시하기, 토마토 가꾸기, 교회 콘서트 가기—이 이제는 실제로 즐기는 것보다는 그냥 해치워야 할 일처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 이제 2년 4개월 정도 됐어요. 제가 다시 전면적인 운영 리더십에 불려 들어갔을 때쯤 시작됐고, 그 이후로 계속 이렇게 저랑 함께 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 예전에 즐기시던 일들을 여전히 즐기시나요, 아니면 시간이 지나면서 흥미가 줄어드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 확실히 흥미가 줄었어요. 낚시나 토마토 가꾸는 것 같은 일들은 여전히 좀 하긴 하는데, 예전 같지가 않아요. 실제로 즐기기보다는 그냥 목록에서 체크하는 느낌에 더 가까워요. 대부분의 날이 그냥 회색빛에 밋밋한 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 완전히 정상으로 돌아왔다고 느낀 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 딱히 없었어요. 제가 다시 전면적인 운영 리더십에 불려 들어간 이후로—한 2년 4개월 전부터—거의 계속 그랬어요. 어떤 날은 조금 나을 수도 있지만, 완전히 정상으로 돌아왔다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 식욕이나 체중에 큰 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 식욕이 예전보다 훨씬 자주 이상해요. 점심을 일하면서 그냥 넘기고 잘 신경도 안 쓰다가, 저녁 땐 그냥 음식을 깨작거리게 돼요. 아내가 제 바지가 헐렁해지고 있다고 하는데, 저는 일부러 살을 빼려던 게 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 요즘 불안하거나 초조한 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 불안이라고 딱 말할 수 있을지는 모르겠어요. 공황 같은 느낌이 드는 건 아니에요. 가끔 긴장되긴 하는데, 특별히 요즘 초조하다는 느낌은 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 전혀 슬프거나 가라앉지 않은 날이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 가끔 순간적으로는 있을 수도 있지만, 온전히 하루 종일은 아니에요. 대부분의 날은 이런 회색빛에 밋밋한 느낌이 있어요. 예전에 기대하던 일들—낚시, 토마토 가꾸기, 교회 콘서트 가기—조차 실제로 즐기는 것보다는 그냥 해치워야 할 일처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 여전히 즐거움을 느끼는 활동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 솔직히 별로 없어요. 여전히 낚시하거나 토마토 가꾸는 일을 하고, 교회 콘서트가 있으면 가긴 하는데, 예전처럼 즐겁게 느껴지지 않아요. 실제로 즐거움을 얻기보다는 목록에서 체크하는 느낌에 더 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 이렇게 낮은 기분을 여러 번 겪으셨나요, 아니면 시작된 이후로 계속 꾸준했나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 꽤 꾸준했던 것 같아요. 제가 다시 전면적인 운영 리더십에 불려 들어갔을 때 시작됐는데, 그게 한 2년 4개월 전이에요. 그 이후로 눈에 띄게 나아진 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 여전히 즐거움을 느끼고 기대되는 활동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 딱히 없어요. 그런 일들—낚시, 토마토, 어쩌면 교회 콘서트—은 여전히 하긴 하는데, 예전처럼 기대되지가 않아요. 그냥 해치우는 느낌에 더 가깝고, 그 회색빛 느낌은 대부분의 날 여전히 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 적어도 2주 동안 지속적으로 우울했던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 2주보다 훨씬 길었어요. 오랫동안 대부분의 날에 이 회색빛에 밋밋한 느낌이 있었어요. 예전에 기대하던 일들, 낚시나 토마토 가꾸기, 교회 콘서트 가기조차도 실제로 즐기는 것보다는 체크리스트의 항목처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 여전히 즐기고 기대하는 활동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 별로 없어요. 낚시나 토마토 가꾸는 일은 여전히 하고, 가끔 교회 콘서트도 가는데, 더 이상 예전처럼 기대되지 않아요. 그냥 체크하는 느낌에 더 가깝고, 그 회색빛에 밋밋한 느낌은 대부분의 날 여전히 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분을 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 이렇게 분명하게 떠오르는 이전 시기가 없어요. 가끔 기분 낮은 날들은 있었지만, 이번처럼 눈에 띄는 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분을 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 딱히 그런 것 같지 않아요. 그러니까, 누구나처럼 힘든 시기는 있었지만, 이번처럼 이렇게 오래 이렇게 낮았던 시기는 짚을 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 없었던 것 같아요. 가라앉았던 때는 있었지만, 기억나는 이런 삽화는 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 딱히 짚을 만한 게 없어요. 인생의 여러 시기에 가라앉은 적은 있지만, 이번과 비슷하게 느껴지는 이전 삽화는 기억나지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 딱히 명확한 예가 없어요. 예전에 가라앉은 적은 있었지만, 그때 이번과 비슷한 다른 삽화가 있었다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 2년 4개월 전에 이 상태가 시작된 이후로 적어도 2개월 동안 완전히 정상으로 돌아왔다고 느낀 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 없었던 것 같아요. 제가 다시 전면적인 운영 리더십에 불려 들어간 이후로, 한 2년 4개월 전부터, 꽤 꾸준히 이어져 왔어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이런 식의 우울 삽화를 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 딱히 그런 것 같지 않아요. 예전에 힘든 시기는 있었지만, 그 전에 이번과 비슷했던 걸 짚을 수는 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 지속성 우울장애 (D014)
 인구통계: 성별 남성 / 나이 63 / 직업상태 computer or information systems manager / 최종학력 대학 재학
@@ -575,488 +999,34 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S029
-배경 서술: 클리포드가 파트타임 자문 역할로 서서히 옮겨가던 무렵, 그의 회사는 어려운 클라우드 마이그레이션과 사이버보안 준수 작업 동안 그에게 임시로 다시 전면적인 운영 리더십을 맡아달라고 요청했고, 이는 그가 낚시, 정원 가꾸기, 교회 콘서트, 멘토링을 중심으로 쌓아가던 은퇴 생활의 리듬을 미뤄지게 만들었다. 그는 처음에는 낮은 기분, 수면 변화, 식욕 변화, 피로감을 다시 필요한 사람이 된 것에서 오는 평범한 부담으로 여겼지만, 마이그레이션이 안정된 이후에도 이 패턴은 2년 4개월 동안 계속되었다. 그의 손상 정도는 경미하지만 눈에 띄는 수준으로 유지되었다: 그는 여전히 필수적인 의무는 수행했지만, 정기적인 진료 예약을 놓치고, 정원을 방치했으며, 평소 즐기던 지역사회 활동 중 일부에서 스스로 물러나는 모습을 보였다. 직장 건강검진과 1차 진료의와의 대화를 통해 이 지속적인 경과가 단순한 업무 피로 이상이라는 것을 깨달은 후, 그는 스스로 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 정말 많이 피곤해서예요, 정상적인 수준 이상으로요. 잠은 잘 자고 직장에서도 여전히 잘 해내고 있는데, 하루가 제대로 시작되기도 전에 배터리가 낮은 상태로 돌아가고 있는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요즘 슬프거나 가라앉는 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네... 그런 것 같아요. 항상 울고 있는 건 아니지만, 꽤 오랫동안 대부분의 날이 뭔가 회색빛에 밋밋하게 느껴졌어요. 예전에 기대하던 일들—낚시하기, 토마토 가꾸기, 교회 콘서트 가기—이 이제는 실제로 즐기는 것보다는 그냥 해치워야 할 일처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 이제 2년 4개월 정도 됐어요. 제가 다시 전면적인 운영 리더십에 불려 들어갔을 때쯤 시작됐고, 그 이후로 계속 이렇게 저랑 함께 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 예전에 즐기시던 일들을 여전히 즐기시나요, 아니면 시간이 지나면서 흥미가 줄어드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 확실히 흥미가 줄었어요. 낚시나 토마토 가꾸는 것 같은 일들은 여전히 좀 하긴 하는데, 예전 같지가 않아요. 실제로 즐기기보다는 그냥 목록에서 체크하는 느낌에 더 가까워요. 대부분의 날이 그냥 회색빛에 밋밋한 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 상태가 시작된 이후로 완전히 정상으로 돌아왔다고 느낀 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 딱히 없었어요. 제가 다시 전면적인 운영 리더십에 불려 들어간 이후로—한 2년 4개월 전부터—거의 계속 그랬어요. 어떤 날은 조금 나을 수도 있지만, 완전히 정상으로 돌아왔다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 식욕이나 체중에 큰 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 식욕이 예전보다 훨씬 자주 이상해요. 점심을 일하면서 그냥 넘기고 잘 신경도 안 쓰다가, 저녁 땐 그냥 음식을 깨작거리게 돼요. 아내가 제 바지가 헐렁해지고 있다고 하는데, 저는 일부러 살을 빼려던 게 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 요즘 불안하거나 초조한 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 불안이라고 딱 말할 수 있을지는 모르겠어요. 공황 같은 느낌이 드는 건 아니에요. 가끔 긴장되긴 하는데, 특별히 요즘 초조하다는 느낌은 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 전혀 슬프거나 가라앉지 않은 날이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 가끔 순간적으로는 있을 수도 있지만, 온전히 하루 종일은 아니에요. 대부분의 날은 이런 회색빛에 밋밋한 느낌이 있어요. 예전에 기대하던 일들—낚시, 토마토 가꾸기, 교회 콘서트 가기—조차 실제로 즐기는 것보다는 그냥 해치워야 할 일처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 여전히 즐거움을 느끼는 활동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 솔직히 별로 없어요. 여전히 낚시하거나 토마토 가꾸는 일을 하고, 교회 콘서트가 있으면 가긴 하는데, 예전처럼 즐겁게 느껴지지 않아요. 실제로 즐거움을 얻기보다는 목록에서 체크하는 느낌에 더 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 이렇게 낮은 기분을 여러 번 겪으셨나요, 아니면 시작된 이후로 계속 꾸준했나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 꽤 꾸준했던 것 같아요. 제가 다시 전면적인 운영 리더십에 불려 들어갔을 때 시작됐는데, 그게 한 2년 4개월 전이에요. 그 이후로 눈에 띄게 나아진 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 여전히 즐거움을 느끼고 기대되는 활동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 딱히 없어요. 그런 일들—낚시, 토마토, 어쩌면 교회 콘서트—은 여전히 하긴 하는데, 예전처럼 기대되지가 않아요. 그냥 해치우는 느낌에 더 가깝고, 그 회색빛 느낌은 대부분의 날 여전히 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 적어도 2주 동안 지속적으로 우울했던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 2주보다 훨씬 길었어요. 오랫동안 대부분의 날에 이 회색빛에 밋밋한 느낌이 있었어요. 예전에 기대하던 일들, 낚시나 토마토 가꾸기, 교회 콘서트 가기조차도 실제로 즐기는 것보다는 체크리스트의 항목처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 여전히 즐기고 기대하는 활동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 별로 없어요. 낚시나 토마토 가꾸는 일은 여전히 하고, 가끔 교회 콘서트도 가는데, 더 이상 예전처럼 기대되지 않아요. 그냥 체크하는 느낌에 더 가깝고, 그 회색빛에 밋밋한 느낌은 대부분의 날 여전히 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분을 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 잘 모르겠어요. 이렇게 분명하게 떠오르는 이전 시기가 없어요. 가끔 기분 낮은 날들은 있었지만, 이번처럼 눈에 띄는 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분을 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 딱히 그런 것 같지 않아요. 그러니까, 누구나처럼 힘든 시기는 있었지만, 이번처럼 이렇게 오래 이렇게 낮았던 시기는 짚을 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 없었던 것 같아요. 가라앉았던 때는 있었지만, 기억나는 이런 삽화는 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 딱히 짚을 만한 게 없어요. 인생의 여러 시기에 가라앉은 적은 있지만, 이번과 비슷하게 느껴지는 이전 삽화는 기억나지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이렇게 낮은 기분의 시기를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 딱히 명확한 예가 없어요. 예전에 가라앉은 적은 있었지만, 그때 이번과 비슷한 다른 삽화가 있었다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 2년 4개월 전에 이 상태가 시작된 이후로 적어도 2개월 동안 완전히 정상으로 돌아왔다고 느낀 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 없었던 것 같아요. 제가 다시 전면적인 운영 리더십에 불려 들어간 이후로, 한 2년 4개월 전부터, 꽤 꾸준히 이어져 왔어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 2년 4개월 전에 시작된 이번 삽화 전에도 이런 식의 우울 삽화를 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 딱히 그런 것 같지 않아요. 예전에 힘든 시기는 있었지만, 그 전에 이번과 비슷했던 걸 짚을 수는 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 클리포드가 파트타임 자문 역할로 서서히 옮겨가던 무렵, 그의 회사는 어려운 클라우드 마이그레이션과 사이버보안 준수 작업 동안 그에게 임시로 다시 전면적인 운영 리더십을 맡아달라고 요청했고, 이는 그가 낚시, 정원 가꾸기, 교회 콘서트, 멘토링을 중심으로 쌓아가던 은퇴 생활의 리듬을 미뤄지게 만들었다. 그는 처음에는 낮은 기분, 수면 변화, 식욕 변화, 피로감을 다시 필요한 사람이 된 것에서 오는 평범한 부담으로 여겼지만, 마이그레이션이 안정된 이후에도 이 패턴은 2년 4개월 동안 계속되었다. 그의 손상 정도는 경미하지만 눈에 띄는 수준으로 유지되었다: 그는 여전히 필수적인 의무는 수행했지만, 정기적인 진료 예약을 놓치고, 정원을 방치했으며, 평소 즐기던 지역사회 활동 중 일부에서 스스로 물러나는 모습을 보였다. 직장 건강검진과 1차 진료의와의 대화를 통해 이 지속적인 경과가 단순한 업무 피로 이상이라는 것을 깨달은 후, 그는 스스로 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 범불안장애 (D011)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 낮은 자존감: 자신을 무능하거나 무가치하다고 평가하는 지속적인 경향, 만성적으로 낮은 자기평가.; 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1022,11 +1027,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1083</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1083</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
